--- a/artfynd/A 8299-2026 artfynd.xlsx
+++ b/artfynd/A 8299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131473815</v>
+        <v>131473813</v>
       </c>
       <c r="B2" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508969</v>
+        <v>508929</v>
       </c>
       <c r="R2" t="n">
-        <v>7085199</v>
+        <v>7085273</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,11 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre luckig hänglavsrik grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -811,45 +806,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131473262</v>
+        <v>131473815</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodflon, Jmt</t>
+          <t>Guckuflon-Nybodkilen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508946</v>
+        <v>508969</v>
       </c>
       <c r="R3" t="n">
-        <v>7085205</v>
+        <v>7085199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,32 +893,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre luckig hänglavsrik grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131473813</v>
+        <v>131473816</v>
       </c>
       <c r="B4" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -951,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508929</v>
+        <v>508954</v>
       </c>
       <c r="R4" t="n">
-        <v>7085273</v>
+        <v>7085258</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Relativt rikligt med garnlav på flera levande och döda granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,6 +1038,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre luckig hänglavsrik grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1021,12 +1055,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,6 +1075,414 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131473260</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508922</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7085202</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131473261</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508941</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7085195</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131473262</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508946</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7085205</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131473263</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508986</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7085191</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8299-2026 artfynd.xlsx
+++ b/artfynd/A 8299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,6 +949,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1075,6 +1090,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473261</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473262</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,8 +1518,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131473263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>